--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.132398043806152</v>
+        <v>1.3215146821185</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0287978161721</v>
+        <v>1.304679645127966</v>
       </c>
       <c r="E2" t="n">
-        <v>4.857189476150729</v>
+        <v>0.7892932898744933</v>
       </c>
       <c r="F2" t="n">
-        <v>4.964335111223679</v>
+        <v>0.806704455573848</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.92319279410585</v>
+        <v>3.2375188290422</v>
       </c>
       <c r="D3" t="n">
-        <v>21.65374491126853</v>
+        <v>3.518733548081136</v>
       </c>
       <c r="E3" t="n">
-        <v>4.857189476150729</v>
+        <v>0.7892932898744933</v>
       </c>
       <c r="F3" t="n">
-        <v>4.964335111223679</v>
+        <v>0.806704455573848</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.33221841807511</v>
+        <v>2.003985492937205</v>
       </c>
       <c r="D4" t="n">
-        <v>12.23041623906155</v>
+        <v>1.987442638847502</v>
       </c>
       <c r="E4" t="n">
-        <v>4.857189476150729</v>
+        <v>0.7892932898744933</v>
       </c>
       <c r="F4" t="n">
-        <v>4.964335111223679</v>
+        <v>0.806704455573848</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.931951072756925</v>
+        <v>1.288942049323</v>
       </c>
       <c r="D5" t="n">
-        <v>15.24352938900637</v>
+        <v>2.477073525713536</v>
       </c>
       <c r="E5" t="n">
-        <v>4.857189476150729</v>
+        <v>0.7892932898744933</v>
       </c>
       <c r="F5" t="n">
-        <v>4.964335111223679</v>
+        <v>0.806704455573848</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
